--- a/output/quickfixclose9_portfolio_daily.xlsx
+++ b/output/quickfixclose9_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>176,851.47</t>
+          <t>175,085.78</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+76.85%</t>
+          <t>+75.09%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>182,940  (+82.94%)</t>
+          <t>181,311  (+81.31%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,505  (6.1 pts of return)</t>
+          <t>3,694  (6.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>3.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,191  (-1.27%)</t>
+          <t>-1,202  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5727,22 +5727,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>176851.47</v>
+        <v>177005.31</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>6402.25</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>170603.06</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>177005.31</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6402.25</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>170603.06</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>175085.78</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>176851.47</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>175085.78</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,829); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9939,7 @@
         <v>-30.5</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>202564.25</v>
+        <v>199869.7</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9915,14 +9963,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>173082.27</v>
@@ -9931,14 +9987,14 @@
         <v>2405.84</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>-96.23</v>
+        <v>-2790.78</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>202594.75</v>
+        <v>199900.2</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose9_portfolio_daily.xlsx
+++ b/output/quickfixclose9_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>175,085.78</t>
+          <t>208,432.06</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+75.09%</t>
+          <t>+108.43%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>181,311  (+81.31%)</t>
+          <t>215,855  (+115.86%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,694  (6.2 pts of return)</t>
+          <t>3,774  (7.4 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.8x</t>
+          <t>5.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.3 bars</t>
+          <t>4.4 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+7.64R  (best +24.20R)</t>
+          <t>+7.88R  (best +24.20R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,244  (+7.64%)</t>
+          <t>8,098  (+7.88%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5775,22 +5775,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>175085.78</v>
+        <v>175176.55</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>-0</v>
+        <v>4825.73</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>175085.78</v>
+        <v>170350.82</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,829); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-1,829)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>175176.55</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>9885.32</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>165291.23</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 1,704); Nasdaq_100_E_mini short (risk 1,686); S_P_500_E_mini short (risk 1,670)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>208432.06</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>208432.06</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,653)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+22,869); Corn_CBOT_Futures exit_close (+10,415); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9834,14 +9894,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>9</v>
+      </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>14.113</v>
       </c>
       <c r="G79" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.019</v>
+        <v>14.075</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>180505.19</v>
@@ -9849,15 +9917,15 @@
       <c r="J79" s="5" t="n">
         <v>2509.02</v>
       </c>
-      <c r="K79" s="6" t="n">
-        <v>-47.34</v>
+      <c r="K79" s="7" t="n">
+        <v>35315.65</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>202752.83</v>
+        <v>235325.05</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9877,14 +9945,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>9</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>6.525</v>
       </c>
       <c r="G80" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.025</v>
+        <v>6.475</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>177996.17</v>
@@ -9892,15 +9968,15 @@
       <c r="J80" s="5" t="n">
         <v>2474.15</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>-61.85</v>
+      <c r="K80" s="7" t="n">
+        <v>16020.1</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>202690.98</v>
+        <v>251345.15</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9939,7 +10015,7 @@
         <v>-30.5</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>199869.7</v>
+        <v>251300.27</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9990,11 +10066,183 @@
         <v>-2790.78</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>199900.2</v>
+        <v>200009.4</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>192586.47</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2676.95</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>251331.32</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>189909.52</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2639.74</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>251340.61</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>187269.78</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>2603.05</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>251330.77</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>184666.73</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>2566.87</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>251340.76</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose9_portfolio_daily.xlsx
+++ b/output/quickfixclose9_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>208,432.06</t>
+          <t>206,757.49</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+108.43%</t>
+          <t>+106.76%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>215,855  (+115.86%)</t>
+          <t>214,145  (+114.14%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,774  (7.4 pts of return)</t>
+          <t>3,796  (7.4 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.5x</t>
+          <t>5.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,202  (-1.27%)</t>
+          <t>-1,210  (-1.26%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>81% of trading days</t>
+          <t>82% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5831,26 +5831,58 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>208432.06</v>
+        <v>208461.15</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>8304.940000000001</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>200156.21</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,653)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+22,869); Corn_CBOT_Futures exit_close (+10,415)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>206757.49</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>208432.06</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>206757.49</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 1,653)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+22,869); Corn_CBOT_Futures exit_close (+10,415); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,002); NY_Palladium_Futures short (risk 1,982)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-1,664); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10015,7 +10047,7 @@
         <v>-30.5</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>251300.27</v>
+        <v>248698.47</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -10109,7 +10141,7 @@
         <v>-9.289999999999999</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>251331.32</v>
+        <v>248729.52</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10152,7 +10184,7 @@
         <v>-0.15</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>251340.61</v>
+        <v>248760.58</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10195,7 +10227,7 @@
         <v>-0.55</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>251330.77</v>
+        <v>248728.96</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10219,14 +10251,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>184666.73</v>
@@ -10235,12 +10275,98 @@
         <v>2566.87</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>-4.39</v>
+        <v>-2584.42</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>251340.76</v>
+        <v>248760.73</v>
       </c>
       <c r="M86" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>238418.78</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>3314.02</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>248751.63</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>235104.76</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>3267.96</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-12.82</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>248738.81</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
